--- a/docs/Genealogie_MEME.xlsx
+++ b/docs/Genealogie_MEME.xlsx
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
       <c r="O4" s="14" t="s">
         <v>40</v>
@@ -2216,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>40</v>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
       <c r="O6" s="14" t="s">
         <v>40</v>
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
       <c r="O7" s="14" t="s">
         <v>40</v>
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="48" t="s">
-        <v>365</v>
+        <v>39</v>
       </c>
       <c r="O8" s="48" t="s">
         <v>55</v>
@@ -2394,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="48" t="s">
-        <v>365</v>
+        <v>39</v>
       </c>
       <c r="O9" s="48" t="s">
         <v>55</v>
@@ -2429,7 +2429,7 @@
         <v>2</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>40</v>
@@ -2468,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>40</v>
@@ -2511,7 +2511,7 @@
         <v>2</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>40</v>
@@ -2560,7 +2560,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="54" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="O13" s="54" t="s">
         <v>40</v>
@@ -2971,7 +2971,7 @@
         <v>2</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O22" s="10" t="s">
         <v>55</v>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>55</v>
@@ -3061,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="O24" s="10" t="s">
         <v>55</v>
@@ -3108,7 +3108,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>55</v>
@@ -3151,7 +3151,7 @@
         <v>2</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O26" s="10" t="s">
         <v>55</v>
@@ -3198,7 +3198,7 @@
         <v>2</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>55</v>
@@ -3243,7 +3243,7 @@
         <v>2</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="O28" s="10" t="s">
         <v>55</v>
@@ -3284,7 +3284,7 @@
         <v>3</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="O29" s="14" t="s">
         <v>55</v>
@@ -3323,7 +3323,7 @@
         <v>3</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="O30" s="14" t="s">
         <v>55</v>
@@ -3360,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="O31" s="4" t="s">
         <v>55</v>
@@ -3403,7 +3403,7 @@
         <v>3</v>
       </c>
       <c r="N32" s="30" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="O32" s="30" t="s">
         <v>55</v>
@@ -3448,7 +3448,7 @@
         <v>3</v>
       </c>
       <c r="N33" s="30" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="O33" s="30" t="s">
         <v>55</v>
@@ -3487,8 +3487,12 @@
         <v>349</v>
       </c>
       <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
+      <c r="M34" s="14">
+        <v>1</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>49</v>
+      </c>
       <c r="O34" s="14" t="s">
         <v>55</v>
       </c>
@@ -3524,8 +3528,12 @@
       <c r="L35" s="59" t="s">
         <v>305</v>
       </c>
-      <c r="M35" s="59"/>
-      <c r="N35" s="59"/>
+      <c r="M35" s="59">
+        <v>3</v>
+      </c>
+      <c r="N35" s="59" t="s">
+        <v>49</v>
+      </c>
       <c r="O35" s="59" t="s">
         <v>55</v>
       </c>
@@ -3559,8 +3567,12 @@
       <c r="L36" s="59" t="s">
         <v>304</v>
       </c>
-      <c r="M36" s="59"/>
-      <c r="N36" s="59"/>
+      <c r="M36" s="59">
+        <v>3</v>
+      </c>
+      <c r="N36" s="59" t="s">
+        <v>49</v>
+      </c>
       <c r="O36" s="59" t="s">
         <v>55</v>
       </c>
@@ -3591,7 +3603,9 @@
       <c r="K37" s="44"/>
       <c r="L37" s="44"/>
       <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
+      <c r="N37" s="44" t="s">
+        <v>49</v>
+      </c>
       <c r="O37" s="44" t="s">
         <v>55</v>
       </c>
@@ -3622,7 +3636,9 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
+      <c r="N38" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O38" s="4" t="s">
         <v>55</v>
       </c>
@@ -3656,8 +3672,12 @@
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
+      <c r="M39" s="4">
+        <v>2</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O39" s="4" t="s">
         <v>55</v>
       </c>
@@ -3684,7 +3704,9 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
+      <c r="N40" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O40" s="4" t="s">
         <v>55</v>
       </c>
@@ -3888,7 +3910,9 @@
       <c r="L49" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="M49" s="4"/>
+      <c r="M49" s="4">
+        <v>2</v>
+      </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4" t="s">
@@ -3923,8 +3947,12 @@
       <c r="L50" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
+      <c r="M50" s="4">
+        <v>2</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O50" s="4"/>
       <c r="P50" s="4" t="s">
         <v>340</v>
@@ -3953,7 +3981,9 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
+      <c r="N51" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O51" s="4"/>
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
@@ -3972,7 +4002,9 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
+      <c r="N52" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="O52" s="4"/>
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>

--- a/docs/Genealogie_MEME.xlsx
+++ b/docs/Genealogie_MEME.xlsx
@@ -3609,9 +3609,7 @@
       <c r="O37" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="P37" s="44" t="s">
-        <v>313</v>
-      </c>
+      <c r="P37" s="44"/>
       <c r="Q37" s="44"/>
     </row>
     <row r="38">
@@ -3642,9 +3640,7 @@
       <c r="O38" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P38" s="4" t="s">
-        <v>315</v>
-      </c>
+      <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
     <row r="39">
@@ -3681,67 +3677,99 @@
       <c r="O39" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P39" s="4" t="s">
-        <v>317</v>
-      </c>
+      <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+        <v>336</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="4"/>
       <c r="H40" s="5"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="I40" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>368</v>
+      </c>
       <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="L40" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="M40" s="4">
+        <v>2</v>
+      </c>
+      <c r="N40" s="4"/>
       <c r="O40" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P40" s="4" t="s">
-        <v>341</v>
-      </c>
+      <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
     <row r="41">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="F41" s="5"/>
       <c r="G41" s="4"/>
       <c r="H41" s="5"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
+      <c r="I41" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>368</v>
+      </c>
       <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="10" t="s">
-        <v>323</v>
-      </c>
+      <c r="L41" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="M41" s="4">
+        <v>2</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
     <row r="42">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
+      <c r="A42" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F42" s="5"/>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
@@ -3750,11 +3778,13 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="10" t="s">
-        <v>370</v>
-      </c>
+      <c r="N42" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
     <row r="43">
@@ -3773,9 +3803,7 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="36" t="s">
-        <v>328</v>
-      </c>
+      <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
     <row r="44">
@@ -3794,9 +3822,7 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="36" t="s">
-        <v>330</v>
-      </c>
+      <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
     <row r="45">
@@ -3815,9 +3841,7 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="37" t="s">
-        <v>331</v>
-      </c>
+      <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
     <row r="46">
@@ -3836,9 +3860,7 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="37" t="s">
-        <v>332</v>
-      </c>
+      <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
     <row r="47">
@@ -3857,9 +3879,7 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="38" t="s">
-        <v>333</v>
-      </c>
+      <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
     <row r="48">
@@ -3878,101 +3898,53 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="38" t="s">
-        <v>334</v>
-      </c>
+      <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="E49" s="4"/>
       <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>368</v>
-      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="4"/>
-      <c r="L49" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="M49" s="4">
-        <v>2</v>
-      </c>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="4" t="s">
-        <v>338</v>
-      </c>
+      <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="E50" s="4"/>
       <c r="F50" s="5"/>
       <c r="G50" s="4"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>368</v>
-      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="M50" s="4">
-        <v>2</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="4" t="s">
-        <v>340</v>
-      </c>
+      <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E51" s="4"/>
       <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
@@ -3981,9 +3953,7 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
-      <c r="N51" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
@@ -4002,9 +3972,7 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
@@ -7867,175 +7835,40 @@
       <c r="Q255" s="4"/>
     </row>
     <row r="256">
-      <c r="A256" s="4"/>
-      <c r="B256" s="4"/>
-      <c r="C256" s="4"/>
-      <c r="D256" s="4"/>
-      <c r="E256" s="4"/>
-      <c r="F256" s="5"/>
-      <c r="G256" s="4"/>
-      <c r="H256" s="5"/>
-      <c r="I256" s="4"/>
-      <c r="J256" s="4"/>
-      <c r="K256" s="4"/>
-      <c r="L256" s="4"/>
-      <c r="M256" s="4"/>
-      <c r="N256" s="4"/>
-      <c r="O256" s="4"/>
-      <c r="P256" s="4"/>
-      <c r="Q256" s="4"/>
+      <c r="F256" s="2"/>
+      <c r="H256" s="2"/>
     </row>
     <row r="257">
-      <c r="A257" s="4"/>
-      <c r="B257" s="4"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-      <c r="E257" s="4"/>
-      <c r="F257" s="5"/>
-      <c r="G257" s="4"/>
-      <c r="H257" s="5"/>
-      <c r="I257" s="4"/>
-      <c r="J257" s="4"/>
-      <c r="K257" s="4"/>
-      <c r="L257" s="4"/>
-      <c r="M257" s="4"/>
-      <c r="N257" s="4"/>
-      <c r="O257" s="4"/>
-      <c r="P257" s="4"/>
-      <c r="Q257" s="4"/>
+      <c r="F257" s="2"/>
+      <c r="H257" s="2"/>
     </row>
     <row r="258">
-      <c r="A258" s="4"/>
-      <c r="B258" s="4"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="5"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="5"/>
-      <c r="I258" s="4"/>
-      <c r="J258" s="4"/>
-      <c r="K258" s="4"/>
-      <c r="L258" s="4"/>
-      <c r="M258" s="4"/>
-      <c r="N258" s="4"/>
-      <c r="O258" s="4"/>
-      <c r="P258" s="4"/>
-      <c r="Q258" s="4"/>
+      <c r="F258" s="2"/>
+      <c r="H258" s="2"/>
     </row>
     <row r="259">
-      <c r="A259" s="4"/>
-      <c r="B259" s="4"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-      <c r="E259" s="4"/>
-      <c r="F259" s="5"/>
-      <c r="G259" s="4"/>
-      <c r="H259" s="5"/>
-      <c r="I259" s="4"/>
-      <c r="J259" s="4"/>
-      <c r="K259" s="4"/>
-      <c r="L259" s="4"/>
-      <c r="M259" s="4"/>
-      <c r="N259" s="4"/>
-      <c r="O259" s="4"/>
-      <c r="P259" s="4"/>
-      <c r="Q259" s="4"/>
+      <c r="F259" s="2"/>
+      <c r="H259" s="2"/>
     </row>
     <row r="260">
-      <c r="A260" s="4"/>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-      <c r="E260" s="4"/>
-      <c r="F260" s="5"/>
-      <c r="G260" s="4"/>
-      <c r="H260" s="5"/>
-      <c r="I260" s="4"/>
-      <c r="J260" s="4"/>
-      <c r="K260" s="4"/>
-      <c r="L260" s="4"/>
-      <c r="M260" s="4"/>
-      <c r="N260" s="4"/>
-      <c r="O260" s="4"/>
-      <c r="P260" s="4"/>
-      <c r="Q260" s="4"/>
+      <c r="F260" s="2"/>
+      <c r="H260" s="2"/>
     </row>
     <row r="261">
-      <c r="A261" s="4"/>
-      <c r="B261" s="4"/>
-      <c r="C261" s="4"/>
-      <c r="D261" s="4"/>
-      <c r="E261" s="4"/>
-      <c r="F261" s="5"/>
-      <c r="G261" s="4"/>
-      <c r="H261" s="5"/>
-      <c r="I261" s="4"/>
-      <c r="J261" s="4"/>
-      <c r="K261" s="4"/>
-      <c r="L261" s="4"/>
-      <c r="M261" s="4"/>
-      <c r="N261" s="4"/>
-      <c r="O261" s="4"/>
-      <c r="P261" s="4"/>
-      <c r="Q261" s="4"/>
+      <c r="F261" s="2"/>
+      <c r="H261" s="2"/>
     </row>
     <row r="262">
-      <c r="A262" s="4"/>
-      <c r="B262" s="4"/>
-      <c r="C262" s="4"/>
-      <c r="D262" s="4"/>
-      <c r="E262" s="4"/>
-      <c r="F262" s="5"/>
-      <c r="G262" s="4"/>
-      <c r="H262" s="5"/>
-      <c r="I262" s="4"/>
-      <c r="J262" s="4"/>
-      <c r="K262" s="4"/>
-      <c r="L262" s="4"/>
-      <c r="M262" s="4"/>
-      <c r="N262" s="4"/>
-      <c r="O262" s="4"/>
-      <c r="P262" s="4"/>
-      <c r="Q262" s="4"/>
+      <c r="F262" s="2"/>
+      <c r="H262" s="2"/>
     </row>
     <row r="263">
-      <c r="A263" s="4"/>
-      <c r="B263" s="4"/>
-      <c r="C263" s="4"/>
-      <c r="D263" s="4"/>
-      <c r="E263" s="4"/>
-      <c r="F263" s="5"/>
-      <c r="G263" s="4"/>
-      <c r="H263" s="5"/>
-      <c r="I263" s="4"/>
-      <c r="J263" s="4"/>
-      <c r="K263" s="4"/>
-      <c r="L263" s="4"/>
-      <c r="M263" s="4"/>
-      <c r="N263" s="4"/>
-      <c r="O263" s="4"/>
-      <c r="P263" s="4"/>
-      <c r="Q263" s="4"/>
+      <c r="F263" s="2"/>
+      <c r="H263" s="2"/>
     </row>
     <row r="264">
-      <c r="A264" s="4"/>
-      <c r="B264" s="4"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="5"/>
-      <c r="G264" s="4"/>
-      <c r="H264" s="5"/>
-      <c r="I264" s="4"/>
-      <c r="J264" s="4"/>
-      <c r="K264" s="4"/>
-      <c r="L264" s="4"/>
-      <c r="M264" s="4"/>
-      <c r="N264" s="4"/>
-      <c r="O264" s="4"/>
-      <c r="P264" s="4"/>
-      <c r="Q264" s="4"/>
+      <c r="F264" s="2"/>
+      <c r="H264" s="2"/>
     </row>
     <row r="265">
       <c r="F265" s="2"/>
@@ -8944,42 +8777,6 @@
     <row r="491">
       <c r="F491" s="2"/>
       <c r="H491" s="2"/>
-    </row>
-    <row r="492">
-      <c r="F492" s="2"/>
-      <c r="H492" s="2"/>
-    </row>
-    <row r="493">
-      <c r="F493" s="2"/>
-      <c r="H493" s="2"/>
-    </row>
-    <row r="494">
-      <c r="F494" s="2"/>
-      <c r="H494" s="2"/>
-    </row>
-    <row r="495">
-      <c r="F495" s="2"/>
-      <c r="H495" s="2"/>
-    </row>
-    <row r="496">
-      <c r="F496" s="2"/>
-      <c r="H496" s="2"/>
-    </row>
-    <row r="497">
-      <c r="F497" s="2"/>
-      <c r="H497" s="2"/>
-    </row>
-    <row r="498">
-      <c r="F498" s="2"/>
-      <c r="H498" s="2"/>
-    </row>
-    <row r="499">
-      <c r="F499" s="2"/>
-      <c r="H499" s="2"/>
-    </row>
-    <row r="500">
-      <c r="F500" s="2"/>
-      <c r="H500" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/Genealogie_MEME.xlsx
+++ b/docs/Genealogie_MEME.xlsx
@@ -1150,13 +1150,28 @@
   <si>
     <t>P021;P004;P003</t>
   </si>
+  <si>
+    <t>https://gw.geneanet.org/andrerussier?lang=fr&amp;n=laulagnier&amp;p=marie+marguerite</t>
+  </si>
+  <si>
+    <t>Marie Marguerite</t>
+  </si>
+  <si>
+    <t>18 mai 1920</t>
+  </si>
+  <si>
+    <t>18 septembre1892</t>
+  </si>
+  <si>
+    <t>https://gw.geneanet.org/andrerussier?lang=fr&amp;n=laulagnier&amp;oc=0&amp;p=elize+jeanne+marie&amp;type=tree</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1235,6 +1250,13 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FFFF0000"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1332,7 +1354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1487,6 +1509,17 @@
     <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="7" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" xfId="0"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2359,7 +2392,9 @@
         <v>55</v>
       </c>
       <c r="P8" s="48"/>
-      <c r="Q8" s="50"/>
+      <c r="Q8" s="27" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="47">
       <c r="A9" s="48" t="s">
@@ -2400,7 +2435,9 @@
         <v>55</v>
       </c>
       <c r="P9" s="48"/>
-      <c r="Q9" s="50"/>
+      <c r="Q9" s="27" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
@@ -2566,7 +2603,7 @@
         <v>40</v>
       </c>
       <c r="P13" s="54" t="s">
-        <v>261</v>
+        <v>382</v>
       </c>
       <c r="Q13" s="54" t="s">
         <v>63</v>
@@ -3026,50 +3063,50 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="1" s="9">
-      <c r="A24" s="10" t="s">
+    <row r="24" customFormat="1" s="67">
+      <c r="A24" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="64" t="s">
+        <v>379</v>
+      </c>
+      <c r="C24" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="64"/>
+      <c r="E24" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="I24" s="10" t="s">
+      <c r="F24" s="68" t="s">
+        <v>381</v>
+      </c>
+      <c r="G24" s="64"/>
+      <c r="H24" s="68" t="s">
+        <v>380</v>
+      </c>
+      <c r="I24" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10" t="s">
+      <c r="K24" s="64"/>
+      <c r="L24" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="64">
         <v>2</v>
       </c>
-      <c r="N24" s="10" t="s">
+      <c r="N24" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="P24" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="Q24" s="12" t="s">
+      <c r="Q24" s="64" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3413,50 +3450,50 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" customFormat="1" s="29">
-      <c r="A33" s="30" t="s">
+    <row r="33" customFormat="1" s="65">
+      <c r="A33" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="66" t="s">
         <v>269</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="66" t="s">
         <v>270</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="31" t="s">
+      <c r="F33" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="31" t="s">
+      <c r="G33" s="66"/>
+      <c r="H33" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30" t="s">
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="66" t="s">
         <v>265</v>
       </c>
-      <c r="L33" s="30" t="s">
+      <c r="L33" s="66" t="s">
         <v>307</v>
       </c>
-      <c r="M33" s="30">
+      <c r="M33" s="66">
         <v>3</v>
       </c>
-      <c r="N33" s="30" t="s">
+      <c r="N33" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="O33" s="30" t="s">
+      <c r="O33" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="P33" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q33" s="27" t="s">
+      <c r="P33" s="66" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q33" s="66" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3540,7 +3577,9 @@
       <c r="P35" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="Q35" s="59"/>
+      <c r="Q35" s="27" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="36" customFormat="1" s="58">
       <c r="A36" s="59" t="s">
@@ -3579,7 +3618,9 @@
       <c r="P36" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="Q36" s="59"/>
+      <c r="Q36" s="27" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="37" customFormat="1" s="43">
       <c r="A37" s="44" t="s">
@@ -3610,7 +3651,9 @@
         <v>55</v>
       </c>
       <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
+      <c r="Q37" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
@@ -3641,7 +3684,9 @@
         <v>55</v>
       </c>
       <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="54" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
@@ -3678,7 +3723,9 @@
         <v>55</v>
       </c>
       <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
@@ -3715,7 +3762,9 @@
         <v>55</v>
       </c>
       <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
+      <c r="Q40" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
@@ -3754,7 +3803,9 @@
         <v>55</v>
       </c>
       <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
+      <c r="Q41" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
@@ -3785,7 +3836,9 @@
         <v>55</v>
       </c>
       <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
+      <c r="Q42" s="54" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4"/>

--- a/docs/Genealogie_MEME.xlsx
+++ b/docs/Genealogie_MEME.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registre des personnes" sheetId="1" state="visible" r:id="rId1"/>
@@ -1165,13 +1165,127 @@
   <si>
     <t>https://gw.geneanet.org/andrerussier?lang=fr&amp;n=laulagnier&amp;oc=0&amp;p=elize+jeanne+marie&amp;type=tree</t>
   </si>
+  <si>
+    <t>Type de document</t>
+  </si>
+  <si>
+    <t>Livret Famille</t>
+  </si>
+  <si>
+    <t>livret famille</t>
+  </si>
+  <si>
+    <t>carte identité</t>
+  </si>
+  <si>
+    <t>livret militair</t>
+  </si>
+  <si>
+    <t>livret militaire</t>
+  </si>
+  <si>
+    <t>notaire</t>
+  </si>
+  <si>
+    <t>courrier</t>
+  </si>
+  <si>
+    <t>autre</t>
+  </si>
+  <si>
+    <t>acte religieux</t>
+  </si>
+  <si>
+    <t>acte naissance</t>
+  </si>
+  <si>
+    <t>Liens</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/33YEJ7WG18#VB4EHFSB4IQM</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/J16PCHQ944#apeAQw00a5D4</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/59B6AJ1WF8#WVM4UhKO5wwK</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/VK2M1FP4AM#tttOniW6msj7</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/QK47AVTBE0#sYRXRYgNouVv</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/VDDSEQ3WJ4#vVJX5rDAvOyA</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/G20HVRVKJW#7dTghvDIVagm</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/2K3Q7AC8BR#IMDj5ibQphlT</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/84ZXTY9RKM#kyX0Ln9BiuMD</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/YHM2Q44D64#nDNdqqcX1dKE</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/19HF811QK4#rGIEaSDUA0xQ</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/B77MT581KR#FrKKriLs4aP6</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/FM767X08T4#TvsLDZGbmpfO</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/EQ3XYVFNHC#7gfdMxxfAQU4</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/SB4Q66QNRG#hjzB9Dg8tzcE</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/PY5MYVG39R#sxCEYvIrRpIi</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/EDTWWRM5Q0#1Ie4R1PZID5U</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/FWBRHMG8W4#53VrjWQ9mcMr</t>
+  </si>
+  <si>
+    <t>Au dos/Transcription</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/0B8ZWYNJTW#qBqWIZUdDHVL</t>
+  </si>
+  <si>
+    <t>Marie Marguerite LAULAGNIER act de décé</t>
+  </si>
+  <si>
+    <t>acte décé</t>
+  </si>
+  <si>
+    <t>P036*</t>
+  </si>
+  <si>
+    <t>P024;P036</t>
+  </si>
+  <si>
+    <t>P024;P035;P036</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1257,6 +1371,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1354,7 +1475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1520,6 +1641,8 @@
     <xf numFmtId="49" applyNumberFormat="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3085,10 +3208,10 @@
         <v>380</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="J24" s="64" t="s">
-        <v>74</v>
+        <v>268</v>
       </c>
       <c r="K24" s="64"/>
       <c r="L24" s="64" t="s">
@@ -8847,10 +8970,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="49.36328125" customWidth="1" min="2" max="2" bestFit="1"/>
-    <col width="16.81640625" customWidth="1" min="3" max="3" bestFit="1"/>
-    <col width="64.90625" customWidth="1" min="4" max="4" bestFit="1"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col width="49.36328125" customWidth="1" min="3" max="3" bestFit="1"/>
+    <col width="16.81640625" customWidth="1" min="4" max="4" bestFit="1"/>
+    <col width="64.90625" customWidth="1" min="5" max="5" bestFit="1"/>
+    <col min="6" max="6" width="49.6328125" customWidth="1" bestFit="1"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col min="8" max="8" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" ht="33.75">
@@ -8858,321 +8984,441 @@
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="70" t="s">
         <v>125</v>
       </c>
       <c r="B2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C2" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="E2" s="63" t="s">
         <v>375</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="70" t="s">
         <v>129</v>
       </c>
       <c r="B3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C3" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>47</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G3" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="70" t="s">
         <v>132</v>
       </c>
       <c r="B4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>200</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>397</v>
+      </c>
+      <c r="G4" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="70" t="s">
         <v>135</v>
       </c>
       <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G5" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="70" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>207</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>399</v>
+      </c>
+      <c r="G6" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="70" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>350</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>400</v>
+      </c>
+      <c r="G7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="70" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>401</v>
+      </c>
+      <c r="G8" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="70" t="s">
         <v>141</v>
       </c>
       <c r="B9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C9" t="s">
         <v>212</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>351</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="70" t="s">
         <v>142</v>
       </c>
       <c r="B10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C10" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>351</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>403</v>
+      </c>
+      <c r="G10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="70" t="s">
         <v>143</v>
       </c>
       <c r="B11" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>404</v>
+      </c>
+      <c r="G11" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="70" t="s">
         <v>144</v>
       </c>
       <c r="B12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C12" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>350</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>405</v>
+      </c>
+      <c r="G12" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="70" t="s">
         <v>145</v>
       </c>
       <c r="B13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C13" t="s">
         <v>221</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>406</v>
+      </c>
+      <c r="G13" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="70" t="s">
         <v>223</v>
       </c>
       <c r="B14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C14" t="s">
         <v>231</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>407</v>
+      </c>
+      <c r="G14" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="70" t="s">
         <v>224</v>
       </c>
       <c r="B15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C15" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>235</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>408</v>
+      </c>
+      <c r="G15" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="70" t="s">
         <v>225</v>
       </c>
       <c r="B16" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16" t="s">
         <v>236</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>376</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>409</v>
+      </c>
+      <c r="G16" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="70" t="s">
         <v>226</v>
       </c>
       <c r="B17" t="s">
+        <v>391</v>
+      </c>
+      <c r="C17" t="s">
         <v>239</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>46</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>410</v>
+      </c>
+      <c r="G17" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="70" t="s">
         <v>227</v>
       </c>
       <c r="B18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>377</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="70" t="s">
         <v>228</v>
       </c>
       <c r="B19" t="s">
+        <v>393</v>
+      </c>
+      <c r="C19" t="s">
         <v>262</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>273</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>412</v>
+      </c>
+      <c r="G19" t="s">
         <v>264</v>
       </c>
     </row>
@@ -9180,1469 +9426,1463 @@
       <c r="A20" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="B20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C20" t="s">
+        <v>416</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E20" t="s">
+        <v>420</v>
+      </c>
+      <c r="F20" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
         <v>230</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22">
-      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23">
-      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24">
-      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25">
-      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26">
-      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27">
-      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28">
-      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29">
-      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30">
-      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31">
-      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32">
-      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33">
-      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34">
-      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35">
-      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36">
-      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37">
-      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
     </row>
     <row r="38">
-      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39">
-      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40">
-      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41">
-      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
     </row>
     <row r="42">
-      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
     </row>
     <row r="43">
-      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44">
-      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45">
-      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46">
-      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="47">
-      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
     </row>
     <row r="48">
-      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
     </row>
     <row r="49">
-      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
     </row>
     <row r="50">
-      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
     </row>
     <row r="51">
-      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
     </row>
     <row r="52">
-      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
     </row>
     <row r="53">
-      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
     </row>
     <row r="54">
-      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
     </row>
     <row r="55">
-      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
     </row>
     <row r="56">
-      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
     </row>
     <row r="57">
-      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
     </row>
     <row r="58">
-      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
     </row>
     <row r="59">
-      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
     </row>
     <row r="60">
-      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
     </row>
     <row r="61">
-      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
     </row>
     <row r="62">
-      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
     </row>
     <row r="63">
-      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
     </row>
     <row r="64">
-      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
     </row>
     <row r="65">
-      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
     </row>
     <row r="66">
-      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
     </row>
     <row r="67">
-      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
     </row>
     <row r="68">
-      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
     </row>
     <row r="69">
-      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
     </row>
     <row r="70">
-      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
     </row>
     <row r="71">
-      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
     </row>
     <row r="72">
-      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
     </row>
     <row r="73">
-      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
     </row>
     <row r="74">
-      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
     </row>
     <row r="75">
-      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
     </row>
     <row r="76">
-      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
     </row>
     <row r="77">
-      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
     </row>
     <row r="78">
-      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
     </row>
     <row r="79">
-      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
     </row>
     <row r="80">
-      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
     </row>
     <row r="81">
-      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
     </row>
     <row r="82">
-      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
     </row>
     <row r="83">
-      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
     </row>
     <row r="84">
-      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
     </row>
     <row r="85">
-      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
     </row>
     <row r="86">
-      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
     </row>
     <row r="87">
-      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
     </row>
     <row r="88">
-      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
     </row>
     <row r="89">
-      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
     </row>
     <row r="90">
-      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
     </row>
     <row r="91">
-      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
     </row>
     <row r="92">
-      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
     </row>
     <row r="93">
-      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
     </row>
     <row r="94">
-      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
     </row>
     <row r="95">
-      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
     </row>
     <row r="96">
-      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
     </row>
     <row r="97">
-      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
     </row>
     <row r="98">
-      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
     </row>
     <row r="99">
-      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
     </row>
     <row r="100">
-      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
     </row>
     <row r="101">
-      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
     </row>
     <row r="102">
-      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
     </row>
     <row r="103">
-      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
     </row>
     <row r="104">
-      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
     </row>
     <row r="105">
-      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
     </row>
     <row r="106">
-      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
     </row>
     <row r="107">
-      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
     </row>
     <row r="108">
-      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
     </row>
     <row r="109">
-      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
     </row>
     <row r="110">
-      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
     </row>
     <row r="111">
-      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
     </row>
     <row r="112">
-      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
     </row>
     <row r="113">
-      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
     </row>
     <row r="114">
-      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
     </row>
     <row r="115">
-      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
     </row>
     <row r="116">
-      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
     </row>
     <row r="117">
-      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
     </row>
     <row r="118">
-      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
     </row>
     <row r="119">
-      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
     </row>
     <row r="120">
-      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
     </row>
     <row r="121">
-      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
     </row>
     <row r="122">
-      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
     </row>
     <row r="123">
-      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
     </row>
     <row r="124">
-      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
     </row>
     <row r="125">
-      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
     </row>
     <row r="126">
-      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
     </row>
     <row r="127">
-      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
     </row>
     <row r="128">
-      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
     </row>
     <row r="129">
-      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
     </row>
     <row r="130">
-      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
     </row>
     <row r="131">
-      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
     </row>
     <row r="132">
-      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
     </row>
     <row r="133">
-      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
     </row>
     <row r="134">
-      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
     </row>
     <row r="135">
-      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
     </row>
     <row r="136">
-      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
     </row>
     <row r="137">
-      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
     </row>
     <row r="138">
-      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
     </row>
     <row r="139">
-      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
     </row>
     <row r="140">
-      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
     </row>
     <row r="141">
-      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
     </row>
     <row r="142">
-      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
     </row>
     <row r="143">
-      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
     </row>
     <row r="144">
-      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
     </row>
     <row r="145">
-      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
     </row>
     <row r="146">
-      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
     </row>
     <row r="147">
-      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
     </row>
     <row r="148">
-      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
     </row>
     <row r="149">
-      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
     </row>
     <row r="150">
-      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
     </row>
     <row r="151">
-      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
     </row>
     <row r="152">
-      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
     </row>
     <row r="153">
-      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
     </row>
     <row r="154">
-      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
     </row>
     <row r="155">
-      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
     </row>
     <row r="156">
-      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
     </row>
     <row r="157">
-      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
     </row>
     <row r="158">
-      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
     </row>
     <row r="159">
-      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
     </row>
     <row r="160">
-      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
     </row>
     <row r="161">
-      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
     </row>
     <row r="162">
-      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
     </row>
     <row r="163">
-      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
     </row>
     <row r="164">
-      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
     </row>
     <row r="165">
-      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
     </row>
     <row r="166">
-      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
     </row>
     <row r="167">
-      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
     </row>
     <row r="168">
-      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
     </row>
     <row r="169">
-      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
     </row>
     <row r="170">
-      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
     </row>
     <row r="171">
-      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
     </row>
     <row r="172">
-      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
     </row>
     <row r="173">
-      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
     </row>
     <row r="174">
-      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
     </row>
     <row r="175">
-      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
     </row>
     <row r="176">
-      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
     </row>
     <row r="177">
-      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
     </row>
     <row r="178">
-      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
     </row>
     <row r="179">
-      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
     </row>
     <row r="180">
-      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
     </row>
     <row r="181">
-      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
     </row>
     <row r="182">
-      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
     </row>
     <row r="183">
-      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
     </row>
     <row r="184">
-      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
     </row>
     <row r="185">
-      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
     </row>
     <row r="186">
-      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
     </row>
     <row r="187">
-      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
     </row>
     <row r="188">
-      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
     </row>
     <row r="189">
-      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
     </row>
     <row r="190">
-      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
     </row>
     <row r="191">
-      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
     </row>
     <row r="192">
-      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
     </row>
     <row r="193">
-      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
     </row>
     <row r="194">
-      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
     </row>
     <row r="195">
-      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
     </row>
     <row r="196">
-      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
     </row>
     <row r="197">
-      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
     </row>
     <row r="198">
-      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
     </row>
     <row r="199">
-      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
     </row>
     <row r="200">
-      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
     </row>
     <row r="201">
-      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
     </row>
     <row r="202">
-      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
     </row>
     <row r="203">
-      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
     </row>
     <row r="204">
-      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
     </row>
     <row r="205">
-      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
     </row>
     <row r="206">
-      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
     </row>
     <row r="207">
-      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
     </row>
     <row r="208">
-      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
     </row>
     <row r="209">
-      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
     </row>
     <row r="210">
-      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
     </row>
     <row r="211">
-      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
     </row>
     <row r="212">
-      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
     </row>
     <row r="213">
-      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
     </row>
     <row r="214">
-      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
     </row>
     <row r="215">
-      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
     </row>
     <row r="216">
-      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
     </row>
     <row r="217">
-      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
     </row>
     <row r="218">
-      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
     </row>
     <row r="219">
-      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
     </row>
     <row r="220">
-      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
     </row>
     <row r="221">
-      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
     </row>
     <row r="222">
-      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
     </row>
     <row r="223">
-      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
     </row>
     <row r="224">
-      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
     </row>
     <row r="225">
-      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
     </row>
     <row r="226">
-      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
     </row>
     <row r="227">
-      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
     </row>
     <row r="228">
-      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
     </row>
     <row r="229">
-      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
     </row>
     <row r="230">
-      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
     </row>
     <row r="231">
-      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
     </row>
     <row r="232">
-      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
     </row>
     <row r="233">
-      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
     </row>
     <row r="234">
-      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
     </row>
     <row r="235">
-      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
     </row>
     <row r="236">
-      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
     </row>
     <row r="237">
-      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
     </row>
     <row r="238">
-      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
     </row>
     <row r="239">
-      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
     </row>
     <row r="240">
-      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
     </row>
     <row r="241">
-      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
     </row>
     <row r="242">
-      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
     </row>
     <row r="243">
-      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
     </row>
     <row r="244">
-      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
     </row>
     <row r="245">
-      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
     </row>
     <row r="246">
-      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
     </row>
     <row r="247">
-      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
     </row>
     <row r="248">
-      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
     </row>
     <row r="249">
-      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
     </row>
     <row r="250">
-      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
     </row>
     <row r="251">
-      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
     </row>
     <row r="252">
-      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
     </row>
     <row r="253">
-      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
     </row>
     <row r="254">
-      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
     </row>
     <row r="255">
-      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
     </row>
     <row r="256">
-      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
     </row>
     <row r="257">
-      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
     </row>
     <row r="258">
-      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
     </row>
     <row r="259">
-      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
     </row>
     <row r="260">
-      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
     </row>
     <row r="261">
-      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
     </row>
     <row r="262">
-      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
     </row>
     <row r="263">
-      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
     </row>
     <row r="264">
-      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
     </row>
     <row r="265">
-      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
     </row>
     <row r="266">
-      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
     </row>
     <row r="267">
-      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
     </row>
     <row r="268">
-      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
     </row>
     <row r="269">
-      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
     </row>
     <row r="270">
-      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
     </row>
     <row r="271">
-      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
     </row>
     <row r="272">
-      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
     </row>
     <row r="273">
-      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
     </row>
     <row r="274">
-      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
     </row>
     <row r="275">
-      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
     </row>
     <row r="276">
-      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
     </row>
     <row r="277">
-      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
     </row>
     <row r="278">
-      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
     </row>
     <row r="279">
-      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
     </row>
     <row r="280">
-      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
     </row>
     <row r="281">
-      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
     </row>
     <row r="282">
-      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
     </row>
     <row r="283">
-      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
     </row>
     <row r="284">
-      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
     </row>
     <row r="285">
-      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
     </row>
     <row r="286">
-      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
     </row>
     <row r="287">
-      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
     </row>
     <row r="288">
-      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
     </row>
     <row r="289">
-      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
     </row>
     <row r="290">
-      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
     </row>
     <row r="291">
-      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
     </row>
     <row r="292">
-      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
     </row>
     <row r="293">
-      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
     </row>
     <row r="294">
-      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
     </row>
     <row r="295">
-      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
     </row>
     <row r="296">
-      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
     </row>
     <row r="297">
-      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
     </row>
     <row r="298">
-      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
     </row>
     <row r="299">
-      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
     </row>
     <row r="300">
-      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
     </row>
     <row r="301">
-      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
     </row>
     <row r="302">
-      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
     </row>
     <row r="303">
-      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
     </row>
     <row r="304">
-      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
     </row>
     <row r="305">
-      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
     </row>
     <row r="306">
-      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
     </row>
     <row r="307">
-      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
     </row>
     <row r="308">
-      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
     </row>
     <row r="309">
-      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
     </row>
     <row r="310">
-      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
     </row>
     <row r="311">
-      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
     </row>
     <row r="312">
-      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
     </row>
     <row r="313">
-      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
     </row>
     <row r="314">
-      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
     </row>
     <row r="315">
-      <c r="C315" s="2"/>
+      <c r="D315" s="2"/>
     </row>
     <row r="316">
-      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
     </row>
     <row r="317">
-      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
     </row>
     <row r="318">
-      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
     </row>
     <row r="319">
-      <c r="C319" s="2"/>
+      <c r="D319" s="2"/>
     </row>
     <row r="320">
-      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
     </row>
     <row r="321">
-      <c r="C321" s="2"/>
+      <c r="D321" s="2"/>
     </row>
     <row r="322">
-      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
     </row>
     <row r="323">
-      <c r="C323" s="2"/>
+      <c r="D323" s="2"/>
     </row>
     <row r="324">
-      <c r="C324" s="2"/>
+      <c r="D324" s="2"/>
     </row>
     <row r="325">
-      <c r="C325" s="2"/>
+      <c r="D325" s="2"/>
     </row>
     <row r="326">
-      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
     </row>
     <row r="327">
-      <c r="C327" s="2"/>
+      <c r="D327" s="2"/>
     </row>
     <row r="328">
-      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
     </row>
     <row r="329">
-      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
     </row>
     <row r="330">
-      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
     </row>
     <row r="331">
-      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
     </row>
     <row r="332">
-      <c r="C332" s="2"/>
+      <c r="D332" s="2"/>
     </row>
     <row r="333">
-      <c r="C333" s="2"/>
+      <c r="D333" s="2"/>
     </row>
     <row r="334">
-      <c r="C334" s="2"/>
+      <c r="D334" s="2"/>
     </row>
     <row r="335">
-      <c r="C335" s="2"/>
+      <c r="D335" s="2"/>
     </row>
     <row r="336">
-      <c r="C336" s="2"/>
+      <c r="D336" s="2"/>
     </row>
     <row r="337">
-      <c r="C337" s="2"/>
+      <c r="D337" s="2"/>
     </row>
     <row r="338">
-      <c r="C338" s="2"/>
+      <c r="D338" s="2"/>
     </row>
     <row r="339">
-      <c r="C339" s="2"/>
+      <c r="D339" s="2"/>
     </row>
     <row r="340">
-      <c r="C340" s="2"/>
+      <c r="D340" s="2"/>
     </row>
     <row r="341">
-      <c r="C341" s="2"/>
+      <c r="D341" s="2"/>
     </row>
     <row r="342">
-      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
     </row>
     <row r="343">
-      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
     </row>
     <row r="344">
-      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
     </row>
     <row r="345">
-      <c r="C345" s="2"/>
+      <c r="D345" s="2"/>
     </row>
     <row r="346">
-      <c r="C346" s="2"/>
+      <c r="D346" s="2"/>
     </row>
     <row r="347">
-      <c r="C347" s="2"/>
+      <c r="D347" s="2"/>
     </row>
     <row r="348">
-      <c r="C348" s="2"/>
+      <c r="D348" s="2"/>
     </row>
     <row r="349">
-      <c r="C349" s="2"/>
+      <c r="D349" s="2"/>
     </row>
     <row r="350">
-      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
     </row>
     <row r="351">
-      <c r="C351" s="2"/>
+      <c r="D351" s="2"/>
     </row>
     <row r="352">
-      <c r="C352" s="2"/>
+      <c r="D352" s="2"/>
     </row>
     <row r="353">
-      <c r="C353" s="2"/>
+      <c r="D353" s="2"/>
     </row>
     <row r="354">
-      <c r="C354" s="2"/>
+      <c r="D354" s="2"/>
     </row>
     <row r="355">
-      <c r="C355" s="2"/>
+      <c r="D355" s="2"/>
     </row>
     <row r="356">
-      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
     </row>
     <row r="357">
-      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
     </row>
     <row r="358">
-      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
     </row>
     <row r="359">
-      <c r="C359" s="2"/>
+      <c r="D359" s="2"/>
     </row>
     <row r="360">
-      <c r="C360" s="2"/>
+      <c r="D360" s="2"/>
     </row>
     <row r="361">
-      <c r="C361" s="2"/>
+      <c r="D361" s="2"/>
     </row>
     <row r="362">
-      <c r="C362" s="2"/>
+      <c r="D362" s="2"/>
     </row>
     <row r="363">
-      <c r="C363" s="2"/>
+      <c r="D363" s="2"/>
     </row>
     <row r="364">
-      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
     </row>
     <row r="365">
-      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
     </row>
     <row r="366">
-      <c r="C366" s="2"/>
+      <c r="D366" s="2"/>
     </row>
     <row r="367">
-      <c r="C367" s="2"/>
+      <c r="D367" s="2"/>
     </row>
     <row r="368">
-      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
     </row>
     <row r="369">
-      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
     </row>
     <row r="370">
-      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
     </row>
     <row r="371">
-      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
     </row>
     <row r="372">
-      <c r="C372" s="2"/>
+      <c r="D372" s="2"/>
     </row>
     <row r="373">
-      <c r="C373" s="2"/>
+      <c r="D373" s="2"/>
     </row>
     <row r="374">
-      <c r="C374" s="2"/>
+      <c r="D374" s="2"/>
     </row>
     <row r="375">
-      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
     </row>
     <row r="376">
-      <c r="C376" s="2"/>
+      <c r="D376" s="2"/>
     </row>
     <row r="377">
-      <c r="C377" s="2"/>
+      <c r="D377" s="2"/>
     </row>
     <row r="378">
-      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
     </row>
     <row r="379">
-      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
     </row>
     <row r="380">
-      <c r="C380" s="2"/>
+      <c r="D380" s="2"/>
     </row>
     <row r="381">
-      <c r="C381" s="2"/>
+      <c r="D381" s="2"/>
     </row>
     <row r="382">
-      <c r="C382" s="2"/>
+      <c r="D382" s="2"/>
     </row>
     <row r="383">
-      <c r="C383" s="2"/>
+      <c r="D383" s="2"/>
     </row>
     <row r="384">
-      <c r="C384" s="2"/>
+      <c r="D384" s="2"/>
     </row>
     <row r="385">
-      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
     </row>
     <row r="386">
-      <c r="C386" s="2"/>
+      <c r="D386" s="2"/>
     </row>
     <row r="387">
-      <c r="C387" s="2"/>
+      <c r="D387" s="2"/>
     </row>
     <row r="388">
-      <c r="C388" s="2"/>
+      <c r="D388" s="2"/>
     </row>
     <row r="389">
-      <c r="C389" s="2"/>
+      <c r="D389" s="2"/>
     </row>
     <row r="390">
-      <c r="C390" s="2"/>
+      <c r="D390" s="2"/>
     </row>
     <row r="391">
-      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
     </row>
     <row r="392">
-      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
     </row>
     <row r="393">
-      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
     </row>
     <row r="394">
-      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
     </row>
     <row r="395">
-      <c r="C395" s="2"/>
+      <c r="D395" s="2"/>
     </row>
     <row r="396">
-      <c r="C396" s="2"/>
+      <c r="D396" s="2"/>
     </row>
     <row r="397">
-      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
     </row>
     <row r="398">
-      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
     </row>
     <row r="399">
-      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
     </row>
     <row r="400">
-      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
     </row>
     <row r="401">
-      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
     </row>
     <row r="402">
-      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
     </row>
     <row r="403">
-      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
     </row>
     <row r="404">
-      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
     </row>
     <row r="405">
-      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
     </row>
     <row r="406">
-      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
     </row>
     <row r="407">
-      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
     </row>
     <row r="408">
-      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
     </row>
     <row r="409">
-      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
     </row>
     <row r="410">
-      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
     </row>
     <row r="411">
-      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
     </row>
     <row r="412">
-      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
     </row>
     <row r="413">
-      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
     </row>
     <row r="414">
-      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
     </row>
     <row r="415">
-      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
     </row>
     <row r="416">
-      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
     </row>
     <row r="417">
-      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
     </row>
     <row r="418">
-      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
     </row>
     <row r="419">
-      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
     </row>
     <row r="420">
-      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
     </row>
     <row r="421">
-      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
     </row>
     <row r="422">
-      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
     </row>
     <row r="423">
-      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
     </row>
     <row r="424">
-      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
     </row>
     <row r="425">
-      <c r="C425" s="2"/>
+      <c r="D425" s="2"/>
     </row>
     <row r="426">
-      <c r="C426" s="2"/>
+      <c r="D426" s="2"/>
     </row>
     <row r="427">
-      <c r="C427" s="2"/>
+      <c r="D427" s="2"/>
     </row>
     <row r="428">
-      <c r="C428" s="2"/>
+      <c r="D428" s="2"/>
     </row>
     <row r="429">
-      <c r="C429" s="2"/>
+      <c r="D429" s="2"/>
     </row>
     <row r="430">
-      <c r="C430" s="2"/>
+      <c r="D430" s="2"/>
     </row>
     <row r="431">
-      <c r="C431" s="2"/>
+      <c r="D431" s="2"/>
     </row>
     <row r="432">
-      <c r="C432" s="2"/>
+      <c r="D432" s="2"/>
     </row>
     <row r="433">
-      <c r="C433" s="2"/>
+      <c r="D433" s="2"/>
     </row>
     <row r="434">
-      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
     </row>
     <row r="435">
-      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
     </row>
     <row r="436">
-      <c r="C436" s="2"/>
+      <c r="D436" s="2"/>
     </row>
     <row r="437">
-      <c r="C437" s="2"/>
+      <c r="D437" s="2"/>
     </row>
     <row r="438">
-      <c r="C438" s="2"/>
+      <c r="D438" s="2"/>
     </row>
     <row r="439">
-      <c r="C439" s="2"/>
+      <c r="D439" s="2"/>
     </row>
     <row r="440">
-      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
     </row>
     <row r="441">
-      <c r="C441" s="2"/>
+      <c r="D441" s="2"/>
     </row>
     <row r="442">
-      <c r="C442" s="2"/>
+      <c r="D442" s="2"/>
     </row>
     <row r="443">
-      <c r="C443" s="2"/>
+      <c r="D443" s="2"/>
     </row>
     <row r="444">
-      <c r="C444" s="2"/>
+      <c r="D444" s="2"/>
     </row>
     <row r="445">
-      <c r="C445" s="2"/>
+      <c r="D445" s="2"/>
     </row>
     <row r="446">
-      <c r="C446" s="2"/>
+      <c r="D446" s="2"/>
     </row>
     <row r="447">
-      <c r="C447" s="2"/>
+      <c r="D447" s="2"/>
     </row>
     <row r="448">
-      <c r="C448" s="2"/>
+      <c r="D448" s="2"/>
     </row>
     <row r="449">
-      <c r="C449" s="2"/>
+      <c r="D449" s="2"/>
     </row>
     <row r="450">
-      <c r="C450" s="2"/>
+      <c r="D450" s="2"/>
     </row>
     <row r="451">
-      <c r="C451" s="2"/>
+      <c r="D451" s="2"/>
     </row>
     <row r="452">
-      <c r="C452" s="2"/>
+      <c r="D452" s="2"/>
     </row>
     <row r="453">
-      <c r="C453" s="2"/>
+      <c r="D453" s="2"/>
     </row>
     <row r="454">
-      <c r="C454" s="2"/>
+      <c r="D454" s="2"/>
     </row>
     <row r="455">
-      <c r="C455" s="2"/>
+      <c r="D455" s="2"/>
     </row>
     <row r="456">
-      <c r="C456" s="2"/>
+      <c r="D456" s="2"/>
     </row>
     <row r="457">
-      <c r="C457" s="2"/>
+      <c r="D457" s="2"/>
     </row>
     <row r="458">
-      <c r="C458" s="2"/>
+      <c r="D458" s="2"/>
     </row>
     <row r="459">
-      <c r="C459" s="2"/>
+      <c r="D459" s="2"/>
     </row>
     <row r="460">
-      <c r="C460" s="2"/>
+      <c r="D460" s="2"/>
     </row>
     <row r="461">
-      <c r="C461" s="2"/>
+      <c r="D461" s="2"/>
     </row>
     <row r="462">
-      <c r="C462" s="2"/>
+      <c r="D462" s="2"/>
     </row>
     <row r="463">
-      <c r="C463" s="2"/>
+      <c r="D463" s="2"/>
     </row>
     <row r="464">
-      <c r="C464" s="2"/>
+      <c r="D464" s="2"/>
     </row>
     <row r="465">
-      <c r="C465" s="2"/>
+      <c r="D465" s="2"/>
     </row>
     <row r="466">
-      <c r="C466" s="2"/>
+      <c r="D466" s="2"/>
     </row>
     <row r="467">
-      <c r="C467" s="2"/>
+      <c r="D467" s="2"/>
     </row>
     <row r="468">
-      <c r="C468" s="2"/>
+      <c r="D468" s="2"/>
     </row>
     <row r="469">
-      <c r="C469" s="2"/>
+      <c r="D469" s="2"/>
     </row>
     <row r="470">
-      <c r="C470" s="2"/>
+      <c r="D470" s="2"/>
     </row>
     <row r="471">
-      <c r="C471" s="2"/>
+      <c r="D471" s="2"/>
     </row>
     <row r="472">
-      <c r="C472" s="2"/>
+      <c r="D472" s="2"/>
     </row>
     <row r="473">
-      <c r="C473" s="2"/>
+      <c r="D473" s="2"/>
     </row>
     <row r="474">
-      <c r="C474" s="2"/>
+      <c r="D474" s="2"/>
     </row>
     <row r="475">
-      <c r="C475" s="2"/>
+      <c r="D475" s="2"/>
     </row>
     <row r="476">
-      <c r="C476" s="2"/>
+      <c r="D476" s="2"/>
     </row>
     <row r="477">
-      <c r="C477" s="2"/>
+      <c r="D477" s="2"/>
     </row>
     <row r="478">
-      <c r="C478" s="2"/>
+      <c r="D478" s="2"/>
     </row>
     <row r="479">
-      <c r="C479" s="2"/>
+      <c r="D479" s="2"/>
     </row>
     <row r="480">
-      <c r="C480" s="2"/>
+      <c r="D480" s="2"/>
     </row>
     <row r="481">
-      <c r="C481" s="2"/>
+      <c r="D481" s="2"/>
     </row>
     <row r="482">
-      <c r="C482" s="2"/>
+      <c r="D482" s="2"/>
     </row>
     <row r="483">
-      <c r="C483" s="2"/>
+      <c r="D483" s="2"/>
     </row>
     <row r="484">
-      <c r="C484" s="2"/>
+      <c r="D484" s="2"/>
     </row>
     <row r="485">
-      <c r="C485" s="2"/>
+      <c r="D485" s="2"/>
     </row>
     <row r="486">
-      <c r="C486" s="2"/>
+      <c r="D486" s="2"/>
     </row>
     <row r="487">
-      <c r="C487" s="2"/>
+      <c r="D487" s="2"/>
     </row>
     <row r="488">
-      <c r="C488" s="2"/>
+      <c r="D488" s="2"/>
     </row>
     <row r="489">
-      <c r="C489" s="2"/>
+      <c r="D489" s="2"/>
     </row>
     <row r="490">
-      <c r="C490" s="2"/>
+      <c r="D490" s="2"/>
     </row>
     <row r="491">
-      <c r="C491" s="2"/>
+      <c r="D491" s="2"/>
     </row>
     <row r="492">
-      <c r="C492" s="2"/>
+      <c r="D492" s="2"/>
     </row>
     <row r="493">
-      <c r="C493" s="2"/>
+      <c r="D493" s="2"/>
     </row>
     <row r="494">
-      <c r="C494" s="2"/>
+      <c r="D494" s="2"/>
     </row>
     <row r="495">
-      <c r="C495" s="2"/>
+      <c r="D495" s="2"/>
     </row>
     <row r="496">
-      <c r="C496" s="2"/>
+      <c r="D496" s="2"/>
     </row>
     <row r="497">
-      <c r="C497" s="2"/>
+      <c r="D497" s="2"/>
     </row>
     <row r="498">
-      <c r="C498" s="2"/>
+      <c r="D498" s="2"/>
     </row>
     <row r="499">
-      <c r="C499" s="2"/>
+      <c r="D499" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" display="D001" r:id="rId1"/>
-    <hyperlink ref="A3" display="D002" r:id="rId2"/>
-    <hyperlink ref="A4" display="D003" r:id="rId3"/>
-    <hyperlink ref="A5" display="D004" r:id="rId4"/>
-    <hyperlink ref="A6" display="D005" r:id="rId5"/>
-    <hyperlink ref="A7" display="D006" r:id="rId6"/>
-    <hyperlink ref="A8" display="D007" r:id="rId7"/>
-    <hyperlink ref="A9" display="D008" r:id="rId8"/>
-    <hyperlink ref="A10" display="D009" r:id="rId9"/>
-    <hyperlink ref="A11" display="D010" r:id="rId10"/>
-    <hyperlink ref="A12" display="D011" r:id="rId11"/>
-    <hyperlink ref="A13" display="D012" r:id="rId12"/>
-    <hyperlink ref="A14" display="D013" r:id="rId13"/>
-    <hyperlink ref="A15" display="D014" r:id="rId14"/>
-    <hyperlink ref="A16" display="D015" r:id="rId15"/>
-    <hyperlink ref="A17" display="D016" r:id="rId16"/>
-    <hyperlink ref="A18" display="D017" r:id="rId17"/>
-    <hyperlink ref="A19" display="D018" r:id="rId18"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
